--- a/WorkBot/refactor-experimental/data/order_archive/Performance Food/Performance Food_Syracuse_20251223.xlsx
+++ b/WorkBot/refactor-experimental/data/order_archive/Performance Food/Performance Food_Syracuse_20251223.xlsx
@@ -602,13 +602,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D9" t="n">
         <v>16.09</v>
       </c>
       <c r="E9" t="n">
-        <v>80.45</v>
+        <v>128.72</v>
       </c>
     </row>
     <row r="10">
